--- a/data/employees.xlsx
+++ b/data/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\خاص احمد جعفر\برمجة\مشاريع\hr_fastapi\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E2CCFA-AC8B-4E26-87A5-CD583E422506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332DAB06-03CB-4D00-9B31-FF96D7F145BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D8371302-35C6-44EF-9061-97F82DCAD271}"/>
   </bookViews>
@@ -1550,66 +1550,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="15">
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1791,6 +1731,66 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <border outline="0">
         <top style="thin">
           <color auto="1"/>
@@ -1837,18 +1837,18 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7331ABE9-D21B-4D40-8202-37AD81799F21}" name="Table1" displayName="Table1" ref="A1:L333" totalsRowShown="0" headerRowBorderDxfId="14" tableBorderDxfId="13" totalsRowBorderDxfId="12">
   <autoFilter ref="A1:L333" xr:uid="{7331ABE9-D21B-4D40-8202-37AD81799F21}"/>
   <tableColumns count="12">
-    <tableColumn id="8" xr3:uid="{C26EDBB9-542D-4C3E-AF3B-53410FB97683}" name="employee_id" dataDxfId="1"/>
-    <tableColumn id="1" xr3:uid="{BF5576FA-00B4-4E50-A7BF-35881AF749CB}" name="national_id" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{95BE0F9E-72DE-4A76-88CF-67744F989746}" name="legacy_code" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{366C2E5B-003D-4D5F-B17A-4B3B0BFF13E4}" name="full_name" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{0EA2DB9D-7D69-4EAC-8BD1-5A72C0C7B600}" name="title" dataDxfId="10"/>
-    <tableColumn id="65" xr3:uid="{FCAE45A1-02C4-4975-AB1D-72AABE947F71}" name="phone" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{800CB8D7-EEC3-476B-86C4-B4F24B35FD05}" name="hire_date" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{7448D032-36B8-40C3-B515-7723613D8C23}" name="site_name" dataDxfId="7"/>
-    <tableColumn id="58" xr3:uid="{7E75475D-E18E-48A4-9460-9A786173BB6A}" name="company_name" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{96DA480B-CC15-464B-A3E9-769D35381794}" name="cost_center" dataDxfId="5"/>
-    <tableColumn id="66" xr3:uid="{6E2FF11F-2D6E-4DCE-B9E4-BB7ADDE1425D}" name="insured" dataDxfId="4"/>
-    <tableColumn id="67" xr3:uid="{A0343A30-BD79-453B-8350-A7989D77B3AC}" name="overnight" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{C26EDBB9-542D-4C3E-AF3B-53410FB97683}" name="employee_id" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{BF5576FA-00B4-4E50-A7BF-35881AF749CB}" name="national_id" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{95BE0F9E-72DE-4A76-88CF-67744F989746}" name="legacy_code" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{366C2E5B-003D-4D5F-B17A-4B3B0BFF13E4}" name="full_name" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{0EA2DB9D-7D69-4EAC-8BD1-5A72C0C7B600}" name="title" dataDxfId="7"/>
+    <tableColumn id="65" xr3:uid="{FCAE45A1-02C4-4975-AB1D-72AABE947F71}" name="phone" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{800CB8D7-EEC3-476B-86C4-B4F24B35FD05}" name="hire_date" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{7448D032-36B8-40C3-B515-7723613D8C23}" name="site_name" dataDxfId="4"/>
+    <tableColumn id="58" xr3:uid="{7E75475D-E18E-48A4-9460-9A786173BB6A}" name="company_name" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{96DA480B-CC15-464B-A3E9-769D35381794}" name="cost_center" dataDxfId="2"/>
+    <tableColumn id="66" xr3:uid="{6E2FF11F-2D6E-4DCE-B9E4-BB7ADDE1425D}" name="insured" dataDxfId="1"/>
+    <tableColumn id="67" xr3:uid="{A0343A30-BD79-453B-8350-A7989D77B3AC}" name="overnight" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
